--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MINNESOTA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MINNESOTA_2018.xlsx
@@ -427,7 +427,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="5">
@@ -841,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="28">
@@ -1201,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="D47">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="48">
@@ -1597,7 +1597,7 @@
         <v>6</v>
       </c>
       <c r="D69">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="70">
@@ -1723,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="D76">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="77">
@@ -1831,7 +1831,7 @@
         <v>6</v>
       </c>
       <c r="D82">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="83">
@@ -1903,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="D86">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="87">
@@ -2443,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="D116">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="117">
@@ -3523,7 +3523,7 @@
         <v>6</v>
       </c>
       <c r="D176">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="177">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C211">
@@ -4495,7 +4495,7 @@
         <v>6</v>
       </c>
       <c r="D230">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="231">
@@ -4693,7 +4693,7 @@
         <v>6</v>
       </c>
       <c r="D241">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="242">
@@ -4837,7 +4837,7 @@
         <v>6</v>
       </c>
       <c r="D249">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="250">
@@ -5179,7 +5179,7 @@
         <v>6</v>
       </c>
       <c r="D268">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="269">
@@ -5539,7 +5539,7 @@
         <v>6</v>
       </c>
       <c r="D288">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="289">
@@ -7087,7 +7087,7 @@
         <v>6</v>
       </c>
       <c r="D374">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="375">
@@ -7105,7 +7105,7 @@
         <v>6</v>
       </c>
       <c r="D375">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="376">
@@ -9049,7 +9049,7 @@
         <v>6</v>
       </c>
       <c r="D483">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="484">
@@ -9283,7 +9283,7 @@
         <v>6</v>
       </c>
       <c r="D496">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="497">
@@ -9427,7 +9427,7 @@
         <v>6</v>
       </c>
       <c r="D504">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="505">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C515">
@@ -10129,7 +10129,7 @@
         <v>6</v>
       </c>
       <c r="D543">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="544">
@@ -10435,7 +10435,7 @@
         <v>6</v>
       </c>
       <c r="D560">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="561">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C567">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C583">
@@ -12757,7 +12757,7 @@
         <v>6</v>
       </c>
       <c r="D689">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="690">
@@ -12901,7 +12901,7 @@
         <v>6</v>
       </c>
       <c r="D697">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="698">
@@ -13279,7 +13279,7 @@
         <v>6</v>
       </c>
       <c r="D718">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="719">
@@ -14017,7 +14017,7 @@
         <v>6</v>
       </c>
       <c r="D759">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="760">
@@ -14683,7 +14683,7 @@
         <v>6</v>
       </c>
       <c r="D796">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="797">
@@ -15169,7 +15169,7 @@
         <v>6</v>
       </c>
       <c r="D823">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="824">
@@ -17419,7 +17419,7 @@
         <v>6</v>
       </c>
       <c r="D948">
-        <v>0.0009837678307919331</v>
+        <v>0.0009837678307919333</v>
       </c>
     </row>
     <row r="949">
